--- a/Result/profitability/6770.xlsx
+++ b/Result/profitability/6770.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM30"/>
+  <dimension ref="A1:AM31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4240,6 +4240,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6770</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>17290</v>
+      </c>
+      <c r="D31" t="n">
+        <v>12401</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4889</v>
+      </c>
+      <c r="F31" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3684</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>21.31%</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>204</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3888</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3291</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.1425</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="X31" t="n">
+        <v>-0.7738095238095238</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.764418377321603</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>-4.121412803532008</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
